--- a/feedback_surveys/013_workforce_consulting_effectiveness_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/013_workforce_consulting_effectiveness_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1364,17 +1364,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>role_2_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>role2</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>role2</t>
+          <t>Department 2</t>
         </is>
       </c>
     </row>
@@ -1386,350 +1386,265 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>department_2</t>
+          <t>department_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Department 2</t>
+          <t>Department 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>department_2_choices</t>
+          <t>impact_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>department_1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Department 1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>department_2_choices</t>
+          <t>impact_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>department_1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Department 1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>impact_2_choices</t>
+          <t>role_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>role3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>role3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>impact_2_choices</t>
+          <t>role_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>role1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>role1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>impact_2_choices</t>
+          <t>department_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>department_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Department 3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>role_3_choices</t>
+          <t>department_3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>role3</t>
+          <t>department_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>role3</t>
+          <t>Department 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>role_3_choices</t>
+          <t>department_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>role1</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>role1</t>
+          <t>Department 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>role_3_choices</t>
+          <t>impact_3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>role1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>role1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>department_3_choices</t>
+          <t>impact_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>department_3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Department 3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>department_3_choices</t>
+          <t>role_4_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>department_1</t>
+          <t>role4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Department 1</t>
+          <t>role4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>department_3_choices</t>
+          <t>role_4_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>department_2</t>
+          <t>role1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Department 2</t>
+          <t>role1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>impact_3_choices</t>
+          <t>role_4_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>role2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>role2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>impact_3_choices</t>
+          <t>department_4_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>department_4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Department 4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>impact_3_choices</t>
+          <t>department_4_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Department 2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>role_4_choices</t>
+          <t>department_4_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>role4</t>
+          <t>department_3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>role4</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>role_4_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>role1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>role1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>role_4_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>role2</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>role2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>department_4_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>department_4</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Department 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>department_4_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>department_2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Department 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>department_4_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>department_3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
         <is>
           <t>Department 3</t>
         </is>
